--- a/results/momentum_rising_2026-10-13.xlsx
+++ b/results/momentum_rising_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,420 +426,420 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>SWRD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>PENG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ARTW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>APOG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>HEPS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>BOLT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>BRBI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>SEZL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>AFYA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SNWV</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SKK</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
@@ -853,49 +853,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>PRHI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
@@ -909,63 +909,84 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>BORR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>LSAK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PBYI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
